--- a/APM_files/152672346/152672346 EXPORT RT&RP Cloud Export_Clone.xlsx
+++ b/APM_files/152672346/152672346 EXPORT RT&RP Cloud Export_Clone.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/darkesthj/Dev/workspace/APM_files/152672346/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6890774-02BC-C94A-B85C-5B7C116E7380}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7EB17F8-91E8-0340-973D-B04F5CCB8FDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="25600" windowHeight="26840" xr2:uid="{2547B3A6-92DE-4DC7-BA33-295CE429FBF9}"/>
+    <workbookView xWindow="25600" yWindow="600" windowWidth="25600" windowHeight="26840" xr2:uid="{2547B3A6-92DE-4DC7-BA33-295CE429FBF9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Hotel ID</t>
   </si>
@@ -44,54 +44,6 @@
     <t>Room Type ID</t>
   </si>
   <si>
-    <t>Max Occupancy</t>
-  </si>
-  <si>
-    <t>People Included In Base Rate</t>
-  </si>
-  <si>
-    <t>Max Adults</t>
-  </si>
-  <si>
-    <t>Max Children</t>
-  </si>
-  <si>
-    <t>Min Age Adults</t>
-  </si>
-  <si>
-    <t>Min Age Children</t>
-  </si>
-  <si>
-    <t>Min Age Infants</t>
-  </si>
-  <si>
-    <t>ARI Room Type</t>
-  </si>
-  <si>
-    <t>Number of Bathrooms - Individual Rooms</t>
-  </si>
-  <si>
-    <t>Number of Bedrooms - Individual Rooms</t>
-  </si>
-  <si>
-    <t>Number of Living Rooms - Individual Rooms</t>
-  </si>
-  <si>
-    <t>BeddingOption1 for Bedroom 1</t>
-  </si>
-  <si>
-    <t>BeddingOption1 for Bedroom 2</t>
-  </si>
-  <si>
-    <t>BeddingOption1 for Bedroom 3</t>
-  </si>
-  <si>
-    <t>BeddingOption1 for Single Space Room</t>
-  </si>
-  <si>
-    <t>BeddingOption1 for Living Room 1</t>
-  </si>
-  <si>
     <t>Smoking</t>
   </si>
   <si>
@@ -131,84 +83,17 @@
     <t>RNS Custom Label</t>
   </si>
   <si>
-    <t>Rate Plan ID</t>
-  </si>
-  <si>
-    <t>Hotel Collect Rate Plan Code</t>
-  </si>
-  <si>
-    <t>Expedia Collect Rate Plan Code</t>
-  </si>
-  <si>
-    <t>Rate Plan Name</t>
-  </si>
-  <si>
-    <t>Rate Plan Type</t>
-  </si>
-  <si>
-    <t>Business Model</t>
-  </si>
-  <si>
-    <t>Rate Plan Status</t>
-  </si>
-  <si>
-    <t>ARI Rate Plan</t>
-  </si>
-  <si>
-    <t>LOS</t>
-  </si>
-  <si>
-    <t>DOA</t>
-  </si>
-  <si>
-    <t>Rate Plan Includes Significant Value</t>
-  </si>
-  <si>
-    <t>Waive Taxes Enabled</t>
-  </si>
-  <si>
-    <t>FeeSet Name</t>
-  </si>
-  <si>
-    <t>Cancellation Policy Name</t>
-  </si>
-  <si>
-    <t>Deposit Required</t>
-  </si>
-  <si>
-    <t>Min Length Of Stay</t>
-  </si>
-  <si>
-    <t>Max Length Of Stay</t>
-  </si>
-  <si>
-    <t>Max Advance Booking Days</t>
-  </si>
-  <si>
-    <t>Expedia Collect Compensation Name</t>
-  </si>
-  <si>
-    <t>Hotel Collect Compensation Name</t>
-  </si>
-  <si>
-    <t>Rate Plan Pricing Model</t>
+    <t>Room Type Name</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C5700"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -219,12 +104,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -240,18 +119,12 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -286,22 +159,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -616,59 +482,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6C0776E-D31D-4196-98AA-2098101953BE}">
-  <dimension ref="A1:BA48"/>
+  <dimension ref="A1:Q48"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="28.83203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="26.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.83203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="27.1640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="38.5" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="37.6640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="40.5" bestFit="1" customWidth="1"/>
-    <col min="22" max="24" width="29" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="36.33203125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="31.6640625" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="15" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="16.1640625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="20.1640625" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="20" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="17" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="4.33203125" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="5" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="33.1640625" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="20" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="23.83203125" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="18" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="25.5" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="34.5" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="32.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" customWidth="1"/>
+    <col min="4" max="5" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.1640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="20" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:53" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -676,280 +508,193 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>35</v>
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>33</v>
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="W1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="X1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AL1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AX1" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="BA1" s="5"/>
-    </row>
-    <row r="2" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="Q1" s="2"/>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>129109</v>
       </c>
     </row>
-    <row r="12" spans="1:53" ht="16" x14ac:dyDescent="0.2">
-      <c r="A12" s="6"/>
-    </row>
-    <row r="13" spans="1:53" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="6"/>
-    </row>
-    <row r="14" spans="1:53" ht="16" x14ac:dyDescent="0.2">
-      <c r="A14" s="6"/>
-    </row>
-    <row r="15" spans="1:53" ht="16" x14ac:dyDescent="0.2">
-      <c r="A15" s="6"/>
-    </row>
-    <row r="16" spans="1:53" ht="16" x14ac:dyDescent="0.2">
-      <c r="A16" s="6"/>
+    <row r="3" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" s="3"/>
+    </row>
+    <row r="4" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+      <c r="A4" s="3"/>
+    </row>
+    <row r="5" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" s="3"/>
+    </row>
+    <row r="6" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+      <c r="A6" s="3"/>
+    </row>
+    <row r="7" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+      <c r="A7" s="3"/>
+    </row>
+    <row r="8" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+      <c r="A8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+      <c r="A9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+      <c r="A10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+      <c r="A11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+      <c r="A12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+      <c r="A13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+      <c r="A14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+      <c r="A15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+      <c r="A16" s="3"/>
     </row>
     <row r="17" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A17" s="6"/>
+      <c r="A17" s="3"/>
     </row>
     <row r="18" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A18" s="6"/>
+      <c r="A18" s="3"/>
     </row>
     <row r="19" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A19" s="6"/>
+      <c r="A19" s="3"/>
     </row>
     <row r="20" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A20" s="6"/>
+      <c r="A20" s="3"/>
     </row>
     <row r="21" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A21" s="6"/>
+      <c r="A21" s="3"/>
     </row>
     <row r="22" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A22" s="6"/>
+      <c r="A22" s="3"/>
     </row>
     <row r="23" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A23" s="6"/>
+      <c r="A23" s="3"/>
     </row>
     <row r="24" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A24" s="6"/>
+      <c r="A24" s="3"/>
     </row>
     <row r="25" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A25" s="6"/>
+      <c r="A25" s="3"/>
     </row>
     <row r="26" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A26" s="6"/>
+      <c r="A26" s="3"/>
     </row>
     <row r="27" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A27" s="6"/>
+      <c r="A27" s="3"/>
     </row>
     <row r="28" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A28" s="6"/>
+      <c r="A28" s="3"/>
     </row>
     <row r="29" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A29" s="6"/>
+      <c r="A29" s="3"/>
     </row>
     <row r="30" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A30" s="6"/>
+      <c r="A30" s="3"/>
     </row>
     <row r="31" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A31" s="6"/>
+      <c r="A31" s="3"/>
     </row>
     <row r="32" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A32" s="6"/>
+      <c r="A32" s="3"/>
     </row>
     <row r="33" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A33" s="6"/>
+      <c r="A33" s="3"/>
     </row>
     <row r="34" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A34" s="6"/>
+      <c r="A34" s="3"/>
     </row>
     <row r="35" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A35" s="6"/>
+      <c r="A35" s="3"/>
     </row>
     <row r="36" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A36" s="6"/>
+      <c r="A36" s="3"/>
     </row>
     <row r="37" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A37" s="6"/>
+      <c r="A37" s="3"/>
     </row>
     <row r="38" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A38" s="6"/>
+      <c r="A38" s="3"/>
     </row>
     <row r="39" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A39" s="6"/>
+      <c r="A39" s="3"/>
     </row>
     <row r="40" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A40" s="6"/>
+      <c r="A40" s="3"/>
     </row>
     <row r="41" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A41" s="6"/>
+      <c r="A41" s="3"/>
     </row>
     <row r="42" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A42" s="6"/>
+      <c r="A42" s="3"/>
     </row>
     <row r="43" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A43" s="6"/>
+      <c r="A43" s="3"/>
     </row>
     <row r="44" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A44" s="6"/>
+      <c r="A44" s="3"/>
     </row>
     <row r="45" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A45" s="6"/>
+      <c r="A45" s="3"/>
     </row>
     <row r="46" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A46" s="6"/>
+      <c r="A46" s="3"/>
     </row>
     <row r="47" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A47" s="6"/>
+      <c r="A47" s="3"/>
     </row>
     <row r="48" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A48" s="6"/>
+      <c r="A48" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
-<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{03ef5274-90b8-4b3f-8a76-b4c36a43e904}" enabled="1" method="Standard" siteId="{61e6eeb3-5fd7-4aaa-ae3c-61e8deb09b79}" contentBits="0" removed="0"/>
-</clbl:labelList>
 </file>